--- a/downloads/singleid-settings-sheet.xlsx
+++ b/downloads/singleid-settings-sheet.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□ このブックに記入　□ CSV別紙で提出　□ SCIM対象グループで管理</t>
+          <t>□ このシートに記入　□ CSV別紙で提出　□ SCIM対象グループで管理</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Entra ID SCIMでユーザ / グループを同期する場合に記入する</t>
+          <t>Microsoft Entra ID SCIMでユーザ / グループを同期する場合に記入する</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>認証方式の制限</t>
+          <t>VPNアクセス &gt; 2要素認証（OTP）のみ許可</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VPNは2要素認証（OTP）のみ許可、無線は証明書認証（EAP-TLS）のみ許可など</t>
+          <t>有効にすると、2要素認証（OTP）以外の認証方式を拒否する</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2267,7 +2267,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>認証方式の制限</t>
+          <t>無線アクセス &gt; 証明書認証（EAP-TLS）のみ許可</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VPNは2要素認証（OTP）のみ許可、無線は証明書認証（EAP-TLS）のみ許可など</t>
+          <t>有効にすると、クライアント証明書認証以外の認証方式を拒否する</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
